--- a/Analysis/mh_recode_file.xlsx
+++ b/Analysis/mh_recode_file.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" firstSheet="3" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="study" sheetId="5" r:id="rId1"/>
@@ -15,6 +15,9 @@
     <sheet name="drop_selected_vars" sheetId="15" r:id="rId6"/>
     <sheet name="model_params" sheetId="16" r:id="rId7"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">selected_vars!$A$1:$N$51</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -25,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1072" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1093" uniqueCount="233">
   <si>
     <t>pos</t>
   </si>
@@ -718,6 +721,12 @@
   </si>
   <si>
     <t>PHQ-9 Depression Severity</t>
+  </si>
+  <si>
+    <t>Date of Interview</t>
+  </si>
+  <si>
+    <t>date_of_interview</t>
   </si>
 </sst>
 </file>
@@ -1256,7 +1265,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.90625" style="3" customWidth="1"/>
@@ -1306,16 +1315,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>29</v>
+        <v>231</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>29</v>
+        <v>232</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>29</v>
+        <v>232</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>125</v>
+        <v>231</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -1323,16 +1332,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -1340,16 +1349,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>74</v>
+        <v>30</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>74</v>
+        <v>30</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -1357,16 +1366,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>32</v>
+        <v>74</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>32</v>
+        <v>74</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>15</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -1374,16 +1383,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>126</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -1391,16 +1400,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>75</v>
+        <v>33</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>75</v>
+        <v>33</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -1408,16 +1417,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -1425,16 +1434,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>223</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -1442,16 +1451,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>37</v>
+        <v>223</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -1459,16 +1468,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>140</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -1476,16 +1485,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>39</v>
+        <v>140</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -1493,16 +1502,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>173</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -1510,16 +1519,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -1527,16 +1536,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -1544,16 +1553,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -1561,16 +1570,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -1578,16 +1587,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -1595,50 +1604,50 @@
         <v>19</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="26" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="4">
         <v>20</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="26" x14ac:dyDescent="0.3">
       <c r="A22" s="4">
         <v>21</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>127</v>
+        <v>189</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
@@ -1646,16 +1655,16 @@
         <v>22</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>166</v>
+        <v>114</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>170</v>
+        <v>127</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
@@ -1663,16 +1672,16 @@
         <v>23</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>129</v>
+        <v>170</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
@@ -1680,50 +1689,50 @@
         <v>24</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="26" x14ac:dyDescent="0.3">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="4">
         <v>25</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="26" x14ac:dyDescent="0.3">
       <c r="A27" s="4">
         <v>26</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
@@ -1731,101 +1740,101 @@
         <v>27</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="39" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="4">
         <v>28</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="39" x14ac:dyDescent="0.3">
       <c r="A30" s="4">
         <v>29</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="39" x14ac:dyDescent="0.3">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="4">
         <v>30</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="26" x14ac:dyDescent="0.3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="39" x14ac:dyDescent="0.3">
       <c r="A32" s="4">
         <v>31</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="26" x14ac:dyDescent="0.3">
       <c r="A33" s="4">
         <v>32</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>115</v>
+        <v>182</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
@@ -1833,33 +1842,33 @@
         <v>33</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>167</v>
+        <v>115</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="39" x14ac:dyDescent="0.3">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="4">
         <v>34</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>190</v>
+        <v>167</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>155</v>
+        <v>169</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="39" x14ac:dyDescent="0.3">
@@ -1867,16 +1876,16 @@
         <v>35</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="39" x14ac:dyDescent="0.3">
@@ -1884,16 +1893,16 @@
         <v>36</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="39" x14ac:dyDescent="0.3">
@@ -1901,67 +1910,67 @@
         <v>37</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" ht="26" x14ac:dyDescent="0.3">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="39" x14ac:dyDescent="0.3">
       <c r="A39" s="4">
         <v>38</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" ht="39" x14ac:dyDescent="0.3">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="26" x14ac:dyDescent="0.3">
       <c r="A40" s="4">
         <v>39</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" ht="26" x14ac:dyDescent="0.3">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="39" x14ac:dyDescent="0.3">
       <c r="A41" s="4">
         <v>40</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="26" x14ac:dyDescent="0.3">
@@ -1969,16 +1978,16 @@
         <v>41</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="26" x14ac:dyDescent="0.3">
@@ -1986,50 +1995,50 @@
         <v>42</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" ht="39.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="26" x14ac:dyDescent="0.3">
       <c r="A44" s="4">
         <v>43</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D44" s="11" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="39.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="4">
         <v>44</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>168</v>
+        <v>199</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
@@ -2037,20 +2046,37 @@
         <v>45</v>
       </c>
       <c r="B46" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="C46" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="D46" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="E46" s="11" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A47" s="4">
+        <v>46</v>
+      </c>
+      <c r="B47" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="C46" s="11" t="s">
+      <c r="C47" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="D46" s="11" t="s">
+      <c r="D47" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="E46" s="11" t="s">
+      <c r="E47" s="11" t="s">
         <v>172</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D1:E1 D47:E1048576">
+  <conditionalFormatting sqref="D48:E1048576 D1:E1">
     <cfRule type="duplicateValues" dxfId="3" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
@@ -2063,7 +2089,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.90625" style="3" customWidth="1"/>
@@ -2113,16 +2139,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>29</v>
+        <v>231</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>29</v>
+        <v>232</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>29</v>
+        <v>232</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>125</v>
+        <v>231</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -2130,16 +2156,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>74</v>
+        <v>29</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>74</v>
+        <v>29</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -2147,16 +2173,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>32</v>
+        <v>74</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>32</v>
+        <v>74</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>15</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -2164,16 +2190,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>126</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -2181,16 +2207,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>144</v>
+        <v>33</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>149</v>
+        <v>33</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>149</v>
+        <v>33</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>154</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -2198,16 +2224,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>34</v>
+        <v>144</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>75</v>
+        <v>149</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>75</v>
+        <v>149</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>138</v>
+        <v>154</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -2215,16 +2241,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -2232,16 +2258,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>223</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -2249,16 +2275,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>183</v>
+        <v>223</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -2266,16 +2292,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -2283,16 +2309,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -2300,16 +2326,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -2317,16 +2343,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -2334,50 +2360,50 @@
         <v>15</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="26" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="4">
         <v>16</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="26" x14ac:dyDescent="0.3">
       <c r="A18" s="4">
         <v>17</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>127</v>
+        <v>189</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -2385,16 +2411,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>174</v>
+        <v>114</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -2402,50 +2428,50 @@
         <v>19</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="26" x14ac:dyDescent="0.3">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="4">
         <v>20</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="26" x14ac:dyDescent="0.3">
       <c r="A22" s="4">
         <v>21</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
@@ -2453,118 +2479,118 @@
         <v>22</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="39" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="4">
         <v>23</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="39" x14ac:dyDescent="0.3">
       <c r="A25" s="4">
         <v>24</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="39" x14ac:dyDescent="0.3">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="4">
         <v>25</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="26" x14ac:dyDescent="0.3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="39" x14ac:dyDescent="0.3">
       <c r="A27" s="4">
         <v>26</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="26" x14ac:dyDescent="0.3">
       <c r="A28" s="4">
         <v>27</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>115</v>
+        <v>182</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="39" x14ac:dyDescent="0.3">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="4">
         <v>28</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>190</v>
+        <v>115</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>155</v>
+        <v>128</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="39" x14ac:dyDescent="0.3">
@@ -2572,16 +2598,16 @@
         <v>29</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="39" x14ac:dyDescent="0.3">
@@ -2589,16 +2615,16 @@
         <v>30</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="39" x14ac:dyDescent="0.3">
@@ -2606,67 +2632,67 @@
         <v>31</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="26" x14ac:dyDescent="0.3">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="39" x14ac:dyDescent="0.3">
       <c r="A33" s="4">
         <v>32</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" ht="39" x14ac:dyDescent="0.3">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="26" x14ac:dyDescent="0.3">
       <c r="A34" s="4">
         <v>33</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="26" x14ac:dyDescent="0.3">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="39" x14ac:dyDescent="0.3">
       <c r="A35" s="4">
         <v>34</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="26" x14ac:dyDescent="0.3">
@@ -2674,16 +2700,16 @@
         <v>35</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="26" x14ac:dyDescent="0.3">
@@ -2691,50 +2717,50 @@
         <v>36</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" ht="39" x14ac:dyDescent="0.3">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="26" x14ac:dyDescent="0.3">
       <c r="A38" s="4">
         <v>37</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="39" x14ac:dyDescent="0.3">
       <c r="A39" s="4">
         <v>38</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>145</v>
+        <v>70</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>150</v>
+        <v>111</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>165</v>
+        <v>199</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
@@ -2742,16 +2768,16 @@
         <v>39</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
@@ -2759,16 +2785,16 @@
         <v>40</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
@@ -2776,20 +2802,37 @@
         <v>41</v>
       </c>
       <c r="B42" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="C42" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="D42" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="E42" s="11" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A43" s="4">
+        <v>42</v>
+      </c>
+      <c r="B43" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="C42" s="11" t="s">
+      <c r="C43" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="D42" s="11" t="s">
+      <c r="D43" s="11" t="s">
         <v>168</v>
       </c>
-      <c r="E42" s="11" t="s">
+      <c r="E43" s="11" t="s">
         <v>171</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D43:E1048576 D1:E1">
+  <conditionalFormatting sqref="D44:E1048576 D1:E1">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
@@ -2802,7 +2845,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N50"/>
+  <dimension ref="A1:N51"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="4.453125" customWidth="1"/>
@@ -2920,36 +2963,36 @@
         <v>203</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>29</v>
+        <v>232</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>125</v>
+        <v>231</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="H3" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="I3" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J3" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="K3" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="L3" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="M3" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="N3" s="11" t="s">
+      <c r="I3" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="J3" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="K3" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="L3" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="M3" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="N3" s="16" t="s">
         <v>12</v>
       </c>
     </row>
@@ -2961,19 +3004,19 @@
         <v>11</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F4" s="16" t="s">
         <v>20</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>209</v>
+        <v>23</v>
       </c>
       <c r="H4" s="16" t="s">
         <v>12</v>
@@ -3005,19 +3048,19 @@
         <v>11</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>74</v>
+        <v>30</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F5" s="16" t="s">
         <v>20</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>23</v>
+        <v>209</v>
       </c>
       <c r="H5" s="16" t="s">
         <v>12</v>
@@ -3052,10 +3095,10 @@
         <v>203</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>32</v>
+        <v>74</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>15</v>
+        <v>123</v>
       </c>
       <c r="F6" s="16" t="s">
         <v>20</v>
@@ -3096,10 +3139,10 @@
         <v>203</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>126</v>
+        <v>15</v>
       </c>
       <c r="F7" s="16" t="s">
         <v>20</v>
@@ -3140,10 +3183,10 @@
         <v>203</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>75</v>
+        <v>33</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="F8" s="16" t="s">
         <v>20</v>
@@ -3184,16 +3227,16 @@
         <v>203</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F9" s="16" t="s">
         <v>20</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>206</v>
+        <v>23</v>
       </c>
       <c r="H9" s="16" t="s">
         <v>12</v>
@@ -3228,10 +3271,10 @@
         <v>203</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>223</v>
+        <v>139</v>
       </c>
       <c r="F10" s="16" t="s">
         <v>20</v>
@@ -3269,19 +3312,19 @@
         <v>11</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>37</v>
+        <v>223</v>
       </c>
       <c r="F11" s="16" t="s">
         <v>20</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="H11" s="16" t="s">
         <v>12</v>
@@ -3316,10 +3359,10 @@
         <v>204</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>140</v>
+        <v>37</v>
       </c>
       <c r="F12" s="16" t="s">
         <v>20</v>
@@ -3360,10 +3403,10 @@
         <v>204</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>39</v>
+        <v>140</v>
       </c>
       <c r="F13" s="16" t="s">
         <v>20</v>
@@ -3404,10 +3447,10 @@
         <v>204</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>173</v>
+        <v>39</v>
       </c>
       <c r="F14" s="16" t="s">
         <v>20</v>
@@ -3445,19 +3488,19 @@
         <v>11</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="F15" s="16" t="s">
         <v>20</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H15" s="16" t="s">
         <v>12</v>
@@ -3465,11 +3508,11 @@
       <c r="I15" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="J15" s="16" t="s">
-        <v>208</v>
+      <c r="J15" s="11" t="s">
+        <v>12</v>
       </c>
       <c r="K15" s="11" t="s">
-        <v>216</v>
+        <v>12</v>
       </c>
       <c r="L15" s="11" t="s">
         <v>12</v>
@@ -3492,10 +3535,10 @@
         <v>203</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F16" s="16" t="s">
         <v>20</v>
@@ -3536,10 +3579,10 @@
         <v>203</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F17" s="16" t="s">
         <v>20</v>
@@ -3580,10 +3623,10 @@
         <v>203</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F18" s="16" t="s">
         <v>20</v>
@@ -3624,10 +3667,10 @@
         <v>203</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F19" s="16" t="s">
         <v>20</v>
@@ -3668,10 +3711,10 @@
         <v>203</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F20" s="16" t="s">
         <v>20</v>
@@ -3701,7 +3744,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="26.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" s="8">
         <v>20</v>
       </c>
@@ -3712,10 +3755,10 @@
         <v>203</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F21" s="16" t="s">
         <v>20</v>
@@ -3745,7 +3788,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:14" ht="26.5" x14ac:dyDescent="0.35">
       <c r="A22" s="8">
         <v>21</v>
       </c>
@@ -3756,28 +3799,28 @@
         <v>203</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>127</v>
+        <v>189</v>
       </c>
       <c r="F22" s="16" t="s">
         <v>20</v>
       </c>
       <c r="G22" s="16" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="H22" s="16" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I22" s="11" t="s">
-        <v>224</v>
-      </c>
-      <c r="J22" s="11" t="s">
-        <v>12</v>
+        <v>12</v>
+      </c>
+      <c r="J22" s="16" t="s">
+        <v>208</v>
       </c>
       <c r="K22" s="11" t="s">
-        <v>12</v>
+        <v>216</v>
       </c>
       <c r="L22" s="11" t="s">
         <v>12</v>
@@ -3786,7 +3829,7 @@
         <v>12</v>
       </c>
       <c r="N22" s="11" t="s">
-        <v>217</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.35">
@@ -3800,10 +3843,10 @@
         <v>203</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>166</v>
+        <v>114</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>170</v>
+        <v>127</v>
       </c>
       <c r="F23" s="16" t="s">
         <v>20</v>
@@ -3815,7 +3858,7 @@
         <v>13</v>
       </c>
       <c r="I23" s="11" t="s">
-        <v>170</v>
+        <v>224</v>
       </c>
       <c r="J23" s="11" t="s">
         <v>12</v>
@@ -3830,7 +3873,7 @@
         <v>12</v>
       </c>
       <c r="N23" s="11" t="s">
-        <v>12</v>
+        <v>217</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.35">
@@ -3844,28 +3887,28 @@
         <v>203</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>129</v>
+        <v>170</v>
       </c>
       <c r="F24" s="16" t="s">
         <v>20</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="H24" s="16" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I24" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J24" s="16" t="s">
-        <v>207</v>
+        <v>170</v>
+      </c>
+      <c r="J24" s="11" t="s">
+        <v>12</v>
       </c>
       <c r="K24" s="11" t="s">
-        <v>216</v>
+        <v>12</v>
       </c>
       <c r="L24" s="11" t="s">
         <v>12</v>
@@ -3888,10 +3931,10 @@
         <v>203</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F25" s="16" t="s">
         <v>20</v>
@@ -3921,7 +3964,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="26.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26" s="8">
         <v>25</v>
       </c>
@@ -3932,10 +3975,10 @@
         <v>203</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F26" s="16" t="s">
         <v>20</v>
@@ -3965,7 +4008,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:14" ht="26.5" x14ac:dyDescent="0.35">
       <c r="A27" s="8">
         <v>26</v>
       </c>
@@ -3976,10 +4019,10 @@
         <v>203</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F27" s="16" t="s">
         <v>20</v>
@@ -4020,10 +4063,10 @@
         <v>203</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F28" s="16" t="s">
         <v>20</v>
@@ -4053,7 +4096,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="26.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29" s="8">
         <v>28</v>
       </c>
@@ -4064,10 +4107,10 @@
         <v>203</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F29" s="16" t="s">
         <v>20</v>
@@ -4097,7 +4140,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:14" ht="26.5" x14ac:dyDescent="0.35">
       <c r="A30" s="8">
         <v>29</v>
       </c>
@@ -4108,10 +4151,10 @@
         <v>203</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F30" s="16" t="s">
         <v>20</v>
@@ -4141,7 +4184,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="39.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A31" s="8">
         <v>30</v>
       </c>
@@ -4152,10 +4195,10 @@
         <v>203</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F31" s="16" t="s">
         <v>20</v>
@@ -4185,7 +4228,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="26.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:14" ht="39.5" x14ac:dyDescent="0.35">
       <c r="A32" s="8">
         <v>31</v>
       </c>
@@ -4196,10 +4239,10 @@
         <v>203</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F32" s="16" t="s">
         <v>20</v>
@@ -4229,7 +4272,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:14" ht="26.5" x14ac:dyDescent="0.35">
       <c r="A33" s="8">
         <v>32</v>
       </c>
@@ -4240,28 +4283,28 @@
         <v>203</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>115</v>
+        <v>182</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="F33" s="16" t="s">
         <v>20</v>
       </c>
       <c r="G33" s="16" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="H33" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="I33" s="16" t="s">
-        <v>225</v>
-      </c>
-      <c r="J33" s="11" t="s">
-        <v>12</v>
+        <v>12</v>
+      </c>
+      <c r="I33" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J33" s="16" t="s">
+        <v>207</v>
       </c>
       <c r="K33" s="11" t="s">
-        <v>12</v>
+        <v>216</v>
       </c>
       <c r="L33" s="11" t="s">
         <v>12</v>
@@ -4270,10 +4313,10 @@
         <v>12</v>
       </c>
       <c r="N33" s="11" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" ht="26.5" x14ac:dyDescent="0.35">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A34" s="8">
         <v>33</v>
       </c>
@@ -4284,10 +4327,10 @@
         <v>203</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>167</v>
+        <v>115</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>169</v>
+        <v>128</v>
       </c>
       <c r="F34" s="16" t="s">
         <v>20</v>
@@ -4298,8 +4341,8 @@
       <c r="H34" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="I34" s="11" t="s">
-        <v>169</v>
+      <c r="I34" s="16" t="s">
+        <v>225</v>
       </c>
       <c r="J34" s="11" t="s">
         <v>12</v>
@@ -4314,7 +4357,7 @@
         <v>12</v>
       </c>
       <c r="N34" s="11" t="s">
-        <v>12</v>
+        <v>217</v>
       </c>
     </row>
     <row r="35" spans="1:14" ht="26.5" x14ac:dyDescent="0.35">
@@ -4328,28 +4371,28 @@
         <v>203</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>190</v>
+        <v>167</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="F35" s="16" t="s">
         <v>20</v>
       </c>
       <c r="G35" s="16" t="s">
-        <v>150</v>
+        <v>205</v>
       </c>
       <c r="H35" s="16" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I35" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J35" s="16" t="s">
-        <v>150</v>
+        <v>169</v>
+      </c>
+      <c r="J35" s="11" t="s">
+        <v>12</v>
       </c>
       <c r="K35" s="11" t="s">
-        <v>216</v>
+        <v>12</v>
       </c>
       <c r="L35" s="11" t="s">
         <v>12</v>
@@ -4361,7 +4404,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="36" spans="1:14" ht="39.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:14" ht="26.5" x14ac:dyDescent="0.35">
       <c r="A36" s="8">
         <v>35</v>
       </c>
@@ -4372,10 +4415,10 @@
         <v>203</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="F36" s="16" t="s">
         <v>20</v>
@@ -4416,10 +4459,10 @@
         <v>203</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="F37" s="16" t="s">
         <v>20</v>
@@ -4460,10 +4503,10 @@
         <v>203</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="F38" s="16" t="s">
         <v>20</v>
@@ -4493,7 +4536,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="39" spans="1:14" ht="26.5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:14" ht="39.5" x14ac:dyDescent="0.35">
       <c r="A39" s="8">
         <v>38</v>
       </c>
@@ -4504,10 +4547,10 @@
         <v>203</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="F39" s="16" t="s">
         <v>20</v>
@@ -4537,7 +4580,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="1:14" ht="39.5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:14" ht="26.5" x14ac:dyDescent="0.35">
       <c r="A40" s="8">
         <v>39</v>
       </c>
@@ -4548,10 +4591,10 @@
         <v>203</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="F40" s="16" t="s">
         <v>20</v>
@@ -4581,7 +4624,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="41" spans="1:14" ht="26.5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:14" ht="39.5" x14ac:dyDescent="0.35">
       <c r="A41" s="8">
         <v>40</v>
       </c>
@@ -4592,10 +4635,10 @@
         <v>203</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="F41" s="16" t="s">
         <v>20</v>
@@ -4636,10 +4679,10 @@
         <v>203</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F42" s="16" t="s">
         <v>20</v>
@@ -4680,10 +4723,10 @@
         <v>203</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F43" s="16" t="s">
         <v>20</v>
@@ -4713,7 +4756,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="44" spans="1:14" ht="39.5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:14" ht="26.5" x14ac:dyDescent="0.35">
       <c r="A44" s="8">
         <v>43</v>
       </c>
@@ -4724,10 +4767,10 @@
         <v>203</v>
       </c>
       <c r="D44" s="11" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F44" s="16" t="s">
         <v>20</v>
@@ -4757,7 +4800,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:14" ht="39.5" x14ac:dyDescent="0.35">
       <c r="A45" s="8">
         <v>44</v>
       </c>
@@ -4768,28 +4811,28 @@
         <v>203</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>168</v>
+        <v>199</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="F45" s="16" t="s">
         <v>20</v>
       </c>
       <c r="G45" s="16" t="s">
-        <v>205</v>
+        <v>150</v>
       </c>
       <c r="H45" s="16" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I45" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="J45" s="11" t="s">
-        <v>12</v>
+        <v>12</v>
+      </c>
+      <c r="J45" s="16" t="s">
+        <v>150</v>
       </c>
       <c r="K45" s="11" t="s">
-        <v>12</v>
+        <v>216</v>
       </c>
       <c r="L45" s="11" t="s">
         <v>12</v>
@@ -4812,10 +4855,10 @@
         <v>203</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F46" s="16" t="s">
         <v>20</v>
@@ -4827,7 +4870,7 @@
         <v>13</v>
       </c>
       <c r="I46" s="11" t="s">
-        <v>226</v>
+        <v>171</v>
       </c>
       <c r="J46" s="11" t="s">
         <v>12</v>
@@ -4842,7 +4885,7 @@
         <v>12</v>
       </c>
       <c r="N46" s="11" t="s">
-        <v>217</v>
+        <v>12</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.35">
@@ -4856,22 +4899,22 @@
         <v>203</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="E47" s="11" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="F47" s="16" t="s">
         <v>20</v>
       </c>
       <c r="G47" s="16" t="s">
-        <v>23</v>
+        <v>205</v>
       </c>
       <c r="H47" s="16" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I47" s="11" t="s">
-        <v>12</v>
+        <v>226</v>
       </c>
       <c r="J47" s="11" t="s">
         <v>12</v>
@@ -4886,7 +4929,7 @@
         <v>12</v>
       </c>
       <c r="N47" s="11" t="s">
-        <v>12</v>
+        <v>217</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.35">
@@ -4894,22 +4937,22 @@
         <v>47</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C48" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="D48" s="15" t="s">
-        <v>200</v>
+      <c r="D48" s="11" t="s">
+        <v>149</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>201</v>
+        <v>154</v>
       </c>
       <c r="F48" s="16" t="s">
         <v>20</v>
       </c>
       <c r="G48" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H48" s="16" t="s">
         <v>12</v>
@@ -4933,7 +4976,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="49" spans="1:14" ht="26.5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A49" s="8">
         <v>48</v>
       </c>
@@ -4944,22 +4987,22 @@
         <v>203</v>
       </c>
       <c r="D49" s="15" t="s">
-        <v>227</v>
+        <v>200</v>
       </c>
       <c r="E49" s="11" t="s">
-        <v>229</v>
+        <v>201</v>
       </c>
       <c r="F49" s="16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G49" s="16" t="s">
-        <v>208</v>
+        <v>24</v>
       </c>
       <c r="H49" s="16" t="s">
         <v>12</v>
       </c>
       <c r="I49" s="11" t="s">
-        <v>229</v>
+        <v>12</v>
       </c>
       <c r="J49" s="11" t="s">
         <v>12</v>
@@ -4977,7 +5020,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="50" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:14" ht="26.5" x14ac:dyDescent="0.35">
       <c r="A50" s="8">
         <v>49</v>
       </c>
@@ -4988,36 +5031,80 @@
         <v>203</v>
       </c>
       <c r="D50" s="15" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F50" s="16" t="s">
         <v>19</v>
       </c>
       <c r="G50" s="16" t="s">
+        <v>208</v>
+      </c>
+      <c r="H50" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="I50" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="J50" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="K50" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="L50" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="M50" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="N50" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="8">
+        <v>50</v>
+      </c>
+      <c r="B51" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="D51" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="E51" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="F51" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G51" s="16" t="s">
         <v>207</v>
       </c>
-      <c r="H50" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="I50" s="11" t="s">
+      <c r="H51" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="I51" s="11" t="s">
         <v>230</v>
       </c>
-      <c r="J50" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="K50" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="L50" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="M50" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="N50" s="11" t="s">
+      <c r="J51" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="K51" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="L51" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="M51" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="N51" s="11" t="s">
         <v>12</v>
       </c>
     </row>
